--- a/Experiment_1_Excel_Formulas.xlsx
+++ b/Experiment_1_Excel_Formulas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rajan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B953AC-CFE1-4038-96CE-22B4AD4EB6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF5DF87-079F-43D9-8881-F5B401FBDE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,41 +61,6 @@
 (300)</t>
   </si>
   <si>
-    <t>Percentage
-(%)</t>
-  </si>
-  <si>
-    <t>Attendance
-(%)</t>
-  </si>
-  <si>
-    <t>Result
-(IF)</t>
-  </si>
-  <si>
-    <t>Grade
-(Nested IF)</t>
-  </si>
-  <si>
-    <t>Scholarship
-Eligible (AND)</t>
-  </si>
-  <si>
-    <t>Needs
-Attention (OR)</t>
-  </si>
-  <si>
-    <t>Not
-Eligible (NOT)</t>
-  </si>
-  <si>
-    <t>Maths:Science
-Ratio (IFERROR)</t>
-  </si>
-  <si>
-    <t>Aarav Sharma</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -132,31 +97,50 @@
     <t>Meera Pillai</t>
   </si>
   <si>
-    <t>Total Marks (SUMIF)</t>
-  </si>
-  <si>
-    <t>Average % (AVERAGEIF)</t>
-  </si>
-  <si>
-    <t>No. of Students (COUNTIF)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Student Result Sheet </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Class-wise Summary </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Student Result Sheet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maths:Science
+Ratio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not
+Eligible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs
+Attention </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scholarship
+Eligible </t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>No. of Students</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average % </t>
+  </si>
+  <si>
+    <t>Total Marks</t>
+  </si>
+  <si>
+    <t>Sanu Sharma</t>
   </si>
 </sst>
 </file>
@@ -173,13 +157,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
@@ -214,13 +191,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
@@ -232,15 +202,27 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -254,13 +236,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
         <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E75B6"/>
+        <fgColor theme="1" tint="0.34998626667073579"/>
         <bgColor rgb="FF0066CC"/>
       </patternFill>
     </fill>
@@ -292,45 +274,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:P32"/>
+  <dimension ref="A2:Q32"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -612,873 +604,895 @@
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-    </row>
-    <row r="3" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-    </row>
-    <row r="4" spans="1:16" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+    </row>
+    <row r="3" spans="1:17" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>88</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>92</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>79</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <f t="shared" ref="G5:G14" si="0">SUM(D5:F5)</f>
         <v>259</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <f t="shared" ref="H5:H14" si="1">ROUND(G5/300*100,2)</f>
         <v>86.33</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>95</v>
       </c>
-      <c r="J5" s="2" t="str">
+      <c r="J5" s="1" t="str">
         <f t="shared" ref="J5:J14" si="2">IF(H5&gt;=40,"Pass","Fail")</f>
         <v>Pass</v>
       </c>
-      <c r="K5" s="2" t="str">
+      <c r="K5" s="1" t="str">
         <f t="shared" ref="K5:K14" si="3">IF(H5&gt;=90,"A+",IF(H5&gt;=75,"A",IF(H5&gt;=60,"B",IF(H5&gt;=40,"C","F"))))</f>
         <v>A</v>
       </c>
-      <c r="L5" s="2" t="str">
+      <c r="L5" s="1" t="str">
         <f t="shared" ref="L5:L14" si="4">IF(AND(H5&gt;=75,I5&gt;=90),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="M5" s="2" t="str">
+      <c r="M5" s="1" t="str">
         <f t="shared" ref="M5:M14" si="5">IF(OR(H5&lt;40,I5&lt;75),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="N5" s="2" t="str">
+      <c r="N5" s="1" t="str">
         <f t="shared" ref="N5:N14" si="6">IF(NOT(L5="Yes"),"No Scholarship","Eligible")</f>
         <v>Eligible</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="1">
         <f t="shared" ref="O5:O14" si="7">IFERROR(ROUND(D5/E5,2),"Data Missing")</f>
         <v>0.96</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="P5" s="9"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3">
         <v>45</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>38</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>52</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>68</v>
       </c>
-      <c r="J6" s="2" t="str">
+      <c r="J6" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="K6" s="2" t="str">
+      <c r="K6" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
-      <c r="L6" s="2" t="str">
+      <c r="L6" s="1" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="M6" s="2" t="str">
+      <c r="M6" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
-      <c r="N6" s="2" t="str">
+      <c r="N6" s="1" t="str">
         <f t="shared" si="6"/>
         <v>No Scholarship</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6" s="1">
         <f t="shared" si="7"/>
         <v>1.18</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="P6" s="9"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
         <v>91</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>95</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>89</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>275</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <f t="shared" si="1"/>
         <v>91.67</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>97</v>
       </c>
-      <c r="J7" s="2" t="str">
+      <c r="J7" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="K7" s="2" t="str">
+      <c r="K7" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A+</v>
       </c>
-      <c r="L7" s="2" t="str">
+      <c r="L7" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
-      <c r="M7" s="2" t="str">
+      <c r="M7" s="1" t="str">
         <f t="shared" si="5"/>
         <v>No</v>
       </c>
-      <c r="N7" s="2" t="str">
+      <c r="N7" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Eligible</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="1">
         <f t="shared" si="7"/>
         <v>0.96</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="P7" s="9"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
         <v>76</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
         <v>81</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
-      <c r="H8" s="5">
-        <f t="shared" si="1"/>
+      <c r="H8" s="4">
+        <f>ROUND(G8/300*100,2)</f>
         <v>52.33</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>88</v>
       </c>
-      <c r="J8" s="2" t="str">
+      <c r="J8" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="K8" s="2" t="str">
+      <c r="K8" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
-      <c r="L8" s="2" t="str">
+      <c r="L8" s="1" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="M8" s="2" t="str">
+      <c r="M8" s="1" t="str">
         <f t="shared" si="5"/>
         <v>No</v>
       </c>
-      <c r="N8" s="2" t="str">
+      <c r="N8" s="1" t="str">
         <f t="shared" si="6"/>
         <v>No Scholarship</v>
       </c>
-      <c r="O8" s="2" t="str">
+      <c r="O8" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Data Missing</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="P8" s="9"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3">
         <v>33</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>29</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>41</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <f t="shared" si="1"/>
         <v>34.33</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>60</v>
       </c>
-      <c r="J9" s="2" t="str">
+      <c r="J9" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Fail</v>
       </c>
-      <c r="K9" s="2" t="str">
+      <c r="K9" s="1" t="str">
         <f t="shared" si="3"/>
         <v>F</v>
       </c>
-      <c r="L9" s="2" t="str">
+      <c r="L9" s="1" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="M9" s="2" t="str">
+      <c r="M9" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
-      <c r="N9" s="2" t="str">
+      <c r="N9" s="1" t="str">
         <f t="shared" si="6"/>
         <v>No Scholarship</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" s="1">
         <f t="shared" si="7"/>
         <v>1.1399999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="P9" s="9"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="3">
         <v>67</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>71</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>65</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <f t="shared" si="1"/>
         <v>67.67</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>82</v>
       </c>
-      <c r="J10" s="2" t="str">
+      <c r="J10" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="K10" s="2" t="str">
+      <c r="K10" s="1" t="str">
         <f t="shared" si="3"/>
         <v>B</v>
       </c>
-      <c r="L10" s="2" t="str">
+      <c r="L10" s="1" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="M10" s="2" t="str">
+      <c r="M10" s="1" t="str">
         <f t="shared" si="5"/>
         <v>No</v>
       </c>
-      <c r="N10" s="2" t="str">
+      <c r="N10" s="1" t="str">
         <f t="shared" si="6"/>
         <v>No Scholarship</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="1">
         <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="P10" s="9"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="3">
         <v>55</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>60</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>58</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <f t="shared" si="0"/>
         <v>173</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <f t="shared" si="1"/>
         <v>57.67</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>74</v>
       </c>
-      <c r="J11" s="2" t="str">
+      <c r="J11" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="K11" s="2" t="str">
+      <c r="K11" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
-      <c r="L11" s="2" t="str">
+      <c r="L11" s="1" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="M11" s="2" t="str">
+      <c r="M11" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
-      <c r="N11" s="2" t="str">
+      <c r="N11" s="1" t="str">
         <f t="shared" si="6"/>
         <v>No Scholarship</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="1">
         <f t="shared" si="7"/>
         <v>0.92</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="P11" s="9"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3">
         <v>96</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>98</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>94</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>99</v>
       </c>
-      <c r="J12" s="2" t="str">
+      <c r="J12" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="K12" s="2" t="str">
+      <c r="K12" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A+</v>
       </c>
-      <c r="L12" s="2" t="str">
+      <c r="L12" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
-      <c r="M12" s="2" t="str">
+      <c r="M12" s="1" t="str">
         <f t="shared" si="5"/>
         <v>No</v>
       </c>
-      <c r="N12" s="2" t="str">
+      <c r="N12" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Eligible</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <f t="shared" si="7"/>
         <v>0.98</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="P12" s="9"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
         <v>40</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>39</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>44</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>65</v>
       </c>
-      <c r="J13" s="2" t="str">
+      <c r="J13" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="K13" s="2" t="str">
+      <c r="K13" s="1" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
-      <c r="L13" s="2" t="str">
+      <c r="L13" s="1" t="str">
         <f t="shared" si="4"/>
         <v>No</v>
       </c>
-      <c r="M13" s="2" t="str">
+      <c r="M13" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
-      <c r="N13" s="2" t="str">
+      <c r="N13" s="1" t="str">
         <f t="shared" si="6"/>
         <v>No Scholarship</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13" s="1">
         <f t="shared" si="7"/>
         <v>1.03</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="P13" s="9"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3">
         <v>82</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>79</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <v>85</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <f t="shared" si="0"/>
         <v>246</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>91</v>
       </c>
-      <c r="J14" s="2" t="str">
+      <c r="J14" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="K14" s="2" t="str">
+      <c r="K14" s="1" t="str">
         <f t="shared" si="3"/>
         <v>A</v>
       </c>
-      <c r="L14" s="2" t="str">
+      <c r="L14" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
-      <c r="M14" s="2" t="str">
+      <c r="M14" s="1" t="str">
         <f t="shared" si="5"/>
         <v>No</v>
       </c>
-      <c r="N14" s="2" t="str">
+      <c r="N14" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Eligible</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O14" s="1">
         <f t="shared" si="7"/>
         <v>1.04</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="P14" s="9"/>
+    </row>
+    <row r="16" spans="1:17" ht="21" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2">
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1">
         <f>SUMIF(C5:C14,A19,G5:G14)</f>
         <v>620</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <f>ROUND(AVERAGEIF(C5:C14,A19,H5:H14),2)</f>
         <v>51.67</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <f>COUNTIF(C5:C14,A19)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="1">
         <f>SUMIF(C5:C14,A20,G5:G14)</f>
         <v>720</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <f>ROUND(AVERAGEIF(C5:C14,A20,H5:H14),2)</f>
         <v>80</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <f>COUNTIF(C5:C14,A20)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1">
         <f>SUMIF(C5:C14,A21,G5:G14)</f>
         <v>622</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <f>ROUND(AVERAGEIF(C5:C14,A21,H5:H14),2)</f>
         <v>69.11</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <f>COUNTIF(C5:C14,A21)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="7"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="7"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="7"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="7"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="7"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="7"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="7"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A24:O24"/>
     <mergeCell ref="A25:O25"/>
